--- a/Assets/Excel/Buff配置表.xlsx
+++ b/Assets/Excel/Buff配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>f_id</t>
   </si>
@@ -38,6 +38,9 @@
     <t>f_description</t>
   </si>
   <si>
+    <t>f_elementType</t>
+  </si>
+  <si>
     <t>f_statusType</t>
   </si>
   <si>
@@ -63,12 +66,20 @@
   </si>
   <si>
     <t>key</t>
+  </si>
+  <si>
+    <t>属性类型
+0：无
+1：火
+2：冰
+3：物理
+4：量子
+5：风</t>
   </si>
   <si>
     <t>状态类型
 1：增益
-2：减益
-3：伤害（可能不需要）</t>
+2：减益</t>
   </si>
   <si>
     <t>状态目标类型
@@ -103,6 +114,18 @@
   </si>
   <si>
     <t>攻击力降低</t>
+  </si>
+  <si>
+    <t>冰蚀</t>
+  </si>
+  <si>
+    <t>回合开始受到固定冰属性伤害</t>
+  </si>
+  <si>
+    <t>风化</t>
+  </si>
+  <si>
+    <t>回合开始受到固定风属性伤害</t>
   </si>
 </sst>
 </file>
@@ -1066,21 +1089,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="2" max="2" width="11.4333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="25.2833333333333" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="22.625" customWidth="1"/>
+    <col min="3" max="4" width="29.9" customWidth="1"/>
+    <col min="5" max="5" width="25.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1108,117 +1131,196 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="22" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="74" customHeight="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="100" customHeight="1" spans="1:10">
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="24" customHeight="1" spans="1:9">
+    <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>10001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
       <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
         <v>2</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="26" customHeight="1" spans="1:9">
+    <row r="6" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
       <c r="A6" s="3">
         <v>10002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
       </c>
       <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>2</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A7" s="3">
+        <v>10003</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A8" s="3">
+        <v>10004</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Buff配置表.xlsx
+++ b/Assets/Excel/Buff配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
   <si>
     <t>f_id</t>
   </si>
@@ -66,6 +66,16 @@
   </si>
   <si>
     <t>key</t>
+  </si>
+  <si>
+    <t>Buff唯一ID
+规则：角色/怪物技能ID + 递增编号</t>
+  </si>
+  <si>
+    <t>Buff名称</t>
+  </si>
+  <si>
+    <t>Buff描述</t>
   </si>
   <si>
     <t>属性类型
@@ -110,10 +120,52 @@
     <t>防御力提高</t>
   </si>
   <si>
+    <t>庇佑II</t>
+  </si>
+  <si>
+    <t>防御力小幅提高</t>
+  </si>
+  <si>
+    <t>庇佑III</t>
+  </si>
+  <si>
+    <t>防御力大幅提高</t>
+  </si>
+  <si>
     <t>恐惧</t>
   </si>
   <si>
     <t>攻击力降低</t>
+  </si>
+  <si>
+    <t>恐惧II</t>
+  </si>
+  <si>
+    <t>攻击力小幅降低</t>
+  </si>
+  <si>
+    <t>恐惧III</t>
+  </si>
+  <si>
+    <t>攻击力大幅降低</t>
+  </si>
+  <si>
+    <t>生机</t>
+  </si>
+  <si>
+    <t>回合开始时恢复固定生命值</t>
+  </si>
+  <si>
+    <t>生机II</t>
+  </si>
+  <si>
+    <t>回合开始时恢复少量生命值</t>
+  </si>
+  <si>
+    <t>生机III</t>
+  </si>
+  <si>
+    <t>回合开始时恢复大量生命值</t>
   </si>
   <si>
     <t>冰蚀</t>
@@ -291,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,6 +365,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,7 +693,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -659,16 +717,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -677,89 +735,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +828,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1089,10 +1150,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="13.45" customWidth="1"/>
     <col min="2" max="2" width="11.4333333333333" customWidth="1"/>
     <col min="3" max="4" width="29.9" customWidth="1"/>
     <col min="5" max="5" width="25.2833333333333" customWidth="1"/>
@@ -1173,42 +1234,51 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="100" customHeight="1" spans="1:10">
-      <c r="D4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
       <c r="A5" s="2">
-        <v>10001</v>
+        <v>101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="6">
         <v>1</v>
       </c>
       <c r="F5" s="2">
@@ -1227,99 +1297,323 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
-      <c r="A6" s="3">
-        <v>10002</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3">
+    <row r="6" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
+      <c r="A6" s="2">
+        <v>111</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>2</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" ht="49" customHeight="1" spans="1:10">
-      <c r="A7" s="3">
-        <v>10003</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>2</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3">
+    <row r="7" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
+      <c r="A7" s="2">
+        <v>121</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2">
         <v>0</v>
       </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="8" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
       <c r="A8" s="3">
-        <v>10004</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
+      <c r="A9" s="3">
+        <v>211</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
+      <c r="A10" s="3">
+        <v>221</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A11" s="2">
+        <v>301</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A12" s="2">
+        <v>311</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A13" s="2">
+        <v>321</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A14" s="4">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A15" s="4">
+        <v>1021</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4">
         <v>5</v>
       </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/Buff配置表.xlsx
+++ b/Assets/Excel/Buff配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>f_id</t>
   </si>
@@ -117,19 +117,19 @@
     <t>庇佑</t>
   </si>
   <si>
-    <t>防御力提高</t>
+    <t>防御力提高，获取固定护盾量</t>
   </si>
   <si>
     <t>庇佑II</t>
   </si>
   <si>
-    <t>防御力小幅提高</t>
+    <t>防御力小幅提高，获取少量护盾</t>
   </si>
   <si>
     <t>庇佑III</t>
   </si>
   <si>
-    <t>防御力大幅提高</t>
+    <t>防御力大幅提高，获取大量护盾</t>
   </si>
   <si>
     <t>恐惧</t>
@@ -178,6 +178,18 @@
   </si>
   <si>
     <t>回合开始受到固定风属性伤害</t>
+  </si>
+  <si>
+    <t>灼烧</t>
+  </si>
+  <si>
+    <t>回合开始受到固定火属性伤害</t>
+  </si>
+  <si>
+    <t>渊涌</t>
+  </si>
+  <si>
+    <t>攻击力大幅提高</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.45" customWidth="1"/>
@@ -1617,6 +1629,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A16" s="4">
+        <v>1041</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4">
+        <v>2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+      <c r="A17" s="4">
+        <v>1051</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>3</v>
+      </c>
+      <c r="I17" s="4">
+        <v>3</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
